--- a/rtos-api-analysis/results/freertos-10.5.1_runtime_info_walltime.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_runtime_info_walltime.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1564</v>
+        <v>43.9596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1988</v>
+        <v>1.1468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3794</v>
+        <v>1.1894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8521</v>
+        <v>3.2114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5147</v>
+        <v>8.1052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7953.2483</v>
+        <v>36002.3751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -739,27 +739,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2029361</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3677</v>
+        <v>2.48</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1608</v>
+        <v>1.7303</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.4167</v>
+        <v>49.041</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84.08280000000001</v>
+        <v>554.6069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2823</v>
+        <v>2.5666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2203</v>
+        <v>0.8669</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7874.9315</v>
+        <v>36006.8727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1075,27 +1075,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>219453</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.9015</v>
+        <v>32.7921</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2063</v>
+        <v>0.7716</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1452</v>
+        <v>1.0608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.14</v>
+        <v>1.0439</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1969</v>
+        <v>1.4114</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1792</v>
+        <v>0.7418</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1646</v>
+        <v>0.7678</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2000.6546</v>
+        <v>11315.5855</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1455,31 +1455,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6892</v>
+        <v>0.6937</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1027321</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1954</v>
+        <v>1.4684</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3816</v>
+        <v>2.0306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1476</v>
+        <v>0.5976</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2458</v>
+        <v>1.8745</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1838</v>
+        <v>1.1554</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.178</v>
+        <v>0.8616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.0291</v>
+        <v>22.9207</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1847</v>
+        <v>4.9574</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.2531</v>
+        <v>60.8007</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2185</v>
+        <v>1.8907</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.224</v>
+        <v>0.8374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9683</v>
+        <v>8.155099999999999</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3991</v>
+        <v>4.8459</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2732</v>
+        <v>1.3554</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2046</v>
+        <v>2.1276</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3426</v>
+        <v>1.7399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.7323</v>
+        <v>11.0216</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1906</v>
+        <v>0.7839</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2733.2019</v>
+        <v>29199.7673</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2367,31 +2367,31 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.6612</v>
+        <v>0.7604</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>3018607</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1266</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3128</v>
+        <v>1.4678</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7823</v>
+        <v>3.1094</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.1248</v>
+        <v>27.4167</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6618.5945</v>
+        <v>14214.5679</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.6462</v>
+        <v>17.6765</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3495</v>
+        <v>2.9991</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12.1002</v>
+        <v>158.2918</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>42.9732</v>
+        <v>333.6154</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.5633</v>
+        <v>50.3107</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3943</v>
+        <v>1.7537</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9.532</v>
+        <v>69.33929999999999</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>7957.902</v>
+        <v>36001.3653</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2995,27 +2995,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1890432</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5918</v>
+        <v>1.4517</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.9456</v>
+        <v>32.5019</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4317.1394</v>
+        <v>36001.049</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3135,26 +3135,26 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.495</v>
+        <v>0.4915</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4381845</t>
+          <t>1707928</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2853</v>
+        <v>1.2486</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5746</v>
+        <v>1.6192</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4201</v>
+        <v>1.9959</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1469</v>
+        <v>0.6908</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2.9329</v>
+        <v>22.6357</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3209</v>
+        <v>2.8595</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>20.9705</v>
+        <v>132.3724</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3202</v>
+        <v>1.0535</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.156</v>
+        <v>1.0046</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.2802</v>
+        <v>1.5407</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>8012.8633</v>
+        <v>36001.9761</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3663,31 +3663,31 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.68</v>
+        <v>0.6795</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2203094</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.1413</v>
+        <v>1.2172</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8.9063</v>
+        <v>171.7572</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>228.3762</v>
+        <v>3224.7176</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.296</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3432</v>
+        <v>1.2201</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1591</v>
+        <v>1.1217</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>149.6233</v>
+        <v>1763.4727</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.162</v>
+        <v>0.8344</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.905</v>
+        <v>36.6374</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>290.8509</v>
+        <v>4627.5087</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1765</v>
+        <v>1.0733</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.3894</v>
+        <v>1.5092</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.2481</v>
+        <v>1.803</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.3283</v>
+        <v>1.5683</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.9448</v>
+        <v>7.6775</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.8305</v>
+        <v>0.8267</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.2298</v>
+        <v>1.7742</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.158</v>
+        <v>1.2068</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.1603</v>
+        <v>0.6874</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8738</v>
+        <v>8.3933</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2009</v>
+        <v>0.8905</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.0042</v>
+        <v>7.4952</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7341</v>
+        <v>4.6343</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>748.5410000000001</v>
+        <v>8263.1914</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8023.0994</v>
+        <v>36010.1238</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>212339</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.215</v>
+        <v>0.7625</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>8027.3526</v>
+        <v>36002.8978</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4911,31 +4911,31 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.674</v>
+        <v>0.6735</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1994314</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2736</v>
+        <v>0.8975</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>8005.7039</v>
+        <v>36001.3498</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5011,27 +5011,27 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32394</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2021298</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>9.6708</v>
+        <v>108.8331</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.2181</v>
+        <v>1.8156</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4888</v>
+        <v>13.1383</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4.7359</v>
+        <v>65.5836</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.278</v>
+        <v>1.3603</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5441.5901</v>
+        <v>36000.6441</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5299,27 +5299,27 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40664</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2544344</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>8.1919</v>
+        <v>37.6732</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.3443</v>
+        <v>1.4641</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>10.3098</v>
+        <v>108.0072</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.1511</v>
+        <v>1.2858</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
